--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484527_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484527_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4543</v>
+        <v>7.3803</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7193</v>
+        <v>5.6205</v>
       </c>
       <c r="F2" t="n">
-        <v>1.735</v>
+        <v>1.7597</v>
       </c>
       <c r="G2" t="n">
         <v>2.6145</v>
@@ -610,13 +610,13 @@
         <v>1.2828</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2405</v>
+        <v>2.1665</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3424</v>
+        <v>1.2436</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8981</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>2.2328</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9634</v>
+        <v>5.771</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6177</v>
+        <v>3.4254</v>
       </c>
       <c r="F3" t="n">
         <v>2.3457</v>
@@ -688,10 +688,10 @@
         <v>1.4661</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0339</v>
+        <v>1.8416</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2074</v>
+        <v>1.0151</v>
       </c>
       <c r="U3" t="n">
         <v>0.8265</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2585</v>
+        <v>3.3095</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2527</v>
+        <v>1.2175</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0059</v>
+        <v>2.092</v>
       </c>
       <c r="G4" t="n">
-        <v>0.175</v>
+        <v>1.0392</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0341</v>
+        <v>0.5903</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.8591</v>
+        <v>0.4489</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3462</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2693</v>
+        <v>0.5294</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.9231</v>
+        <v>0.1606</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1712</v>
+        <v>0.3492</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2351</v>
+        <v>0.0609</v>
       </c>
       <c r="O4" t="n">
-        <v>0.064</v>
+        <v>0.2882</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9163</v>
+        <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2222</v>
+        <v>0.5818</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6395</v>
+        <v>0.4883</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5827</v>
+        <v>0.0935</v>
       </c>
       <c r="V4" t="n">
-        <v>0.945</v>
+        <v>0.9554</v>
       </c>
       <c r="W4" t="n">
-        <v>1.267</v>
+        <v>0.9554</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4315</v>
+        <v>3.2363</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1363</v>
+        <v>2.4039</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2953</v>
+        <v>0.8324</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3934</v>
+        <v>0.175</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8001</v>
+        <v>2.0341</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5933</v>
+        <v>-1.8591</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4107</v>
+        <v>0.3462</v>
       </c>
       <c r="K5" t="n">
-        <v>0.266</v>
+        <v>2.2693</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1447</v>
+        <v>-1.9231</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9827</v>
+        <v>-0.1712</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5341</v>
+        <v>-0.2351</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4486</v>
+        <v>0.064</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6493</v>
+        <v>0.9163</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1377</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2074</v>
+        <v>0.7907</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9303</v>
+        <v>0.4093</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.945</v>
       </c>
       <c r="W5" t="n">
         <v>1.267</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.229</v>
+        <v>1.953</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4343</v>
+        <v>0.0541</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7947</v>
+        <v>1.8989</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0392</v>
+        <v>1.3934</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5903</v>
+        <v>0.8001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4489</v>
+        <v>0.5933</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4107</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5294</v>
+        <v>0.266</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1606</v>
+        <v>0.1447</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3492</v>
+        <v>0.9827</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0609</v>
+        <v>0.5341</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2882</v>
+        <v>0.4486</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R6" t="n">
         <v>1.6493</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4986</v>
+        <v>1.6591</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2949</v>
+        <v>1.1252</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2038</v>
+        <v>0.5339</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9554</v>
+        <v>1.267</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4428</v>
+        <v>1.7511</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3984</v>
+        <v>-0.4368</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8412</v>
+        <v>2.188</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0525</v>
@@ -1000,13 +1000,13 @@
         <v>1.6493</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4106</v>
+        <v>0.8978</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5505</v>
+        <v>0.411</v>
       </c>
       <c r="U7" t="n">
-        <v>0.14</v>
+        <v>0.4868</v>
       </c>
       <c r="V7" t="n">
         <v>1.2566</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2321</v>
+        <v>0.954</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2661</v>
+        <v>-0.8666</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.034</v>
+        <v>1.8206</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1563</v>
+        <v>2.1279</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.065</v>
+        <v>1.3005</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2213</v>
+        <v>0.8274</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1288</v>
+        <v>1.6902</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8111</v>
+        <v>0.8946</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3177</v>
+        <v>0.7956</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9726</v>
+        <v>0.4377</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8762</v>
+        <v>0.4059</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0964</v>
+        <v>0.0318</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9163</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3532</v>
+        <v>0.6874</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0536</v>
+        <v>0.4932</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2996</v>
+        <v>0.1942</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2774</v>
+        <v>-0.945</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2774</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1589</v>
+        <v>0.2085</v>
       </c>
       <c r="E9" t="n">
         <v>0.3532</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1943</v>
+        <v>-0.1447</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2037</v>
@@ -1156,13 +1156,13 @@
         <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0039</v>
+        <v>0.0456</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0369</v>
       </c>
       <c r="U9" t="n">
-        <v>0.033</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0104</v>
+        <v>0.1721</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4608</v>
+        <v>1.0327</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4504</v>
+        <v>-0.8606</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1672</v>
+        <v>1.1563</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7342</v>
+        <v>-0.065</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.433</v>
+        <v>1.2213</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.074</v>
+        <v>2.1288</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2823</v>
+        <v>0.8111</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2084</v>
+        <v>1.3177</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0932</v>
+        <v>-0.9726</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4519</v>
+        <v>-0.8762</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6413</v>
+        <v>-0.0964</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1991</v>
+        <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1959</v>
+        <v>0.2932</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5294</v>
+        <v>-0.1798</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6665</v>
+        <v>0.473</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3219</v>
+        <v>-1.2774</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3219</v>
+        <v>-1.2774</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6492</v>
+        <v>-0.5525</v>
       </c>
       <c r="E11" t="n">
-        <v>0.752</v>
+        <v>-2.557</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4012</v>
+        <v>2.0045</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7955</v>
+        <v>-3.1672</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5617</v>
+        <v>-2.7342</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2338</v>
+        <v>-0.433</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4844</v>
+        <v>-2.074</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4427</v>
+        <v>-2.2823</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0417</v>
+        <v>0.2084</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3112</v>
+        <v>-1.0932</v>
       </c>
       <c r="N11" t="n">
-        <v>0.119</v>
+        <v>-0.4519</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1922</v>
+        <v>-0.6413</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0158</v>
+        <v>1.2828</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>0.733</v>
+        <v>2.1991</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8381</v>
+        <v>1.6538</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4276</v>
+        <v>0.4333</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4105</v>
+        <v>1.2206</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8559</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7559</v>
+        <v>-1.8777</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1305</v>
+        <v>-0.1545</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3746</v>
+        <v>-1.7233</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1279</v>
+        <v>0.7955</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3005</v>
+        <v>0.5617</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8274</v>
+        <v>0.2338</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6902</v>
+        <v>0.4844</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8946</v>
+        <v>0.4427</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7956</v>
+        <v>0.0417</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4377</v>
+        <v>0.3112</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4059</v>
+        <v>0.119</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0318</v>
+        <v>0.1922</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.7489</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8326</v>
+        <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0225</v>
+        <v>0.6095</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.5211</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2517</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.945</v>
+        <v>-1.267</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3011</v>
+        <v>1.5889</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6439</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.755</v>
+        <v>22.3056</v>
       </c>
       <c r="E13" t="n">
-        <v>9.541900000000002</v>
+        <v>10.0924</v>
       </c>
       <c r="F13" t="n">
-        <v>12.2133</v>
+        <v>12.2132</v>
       </c>
       <c r="G13" t="n">
-        <v>6.907399999999999</v>
+        <v>6.9074</v>
       </c>
       <c r="H13" t="n">
         <v>6.105600000000001</v>
@@ -1453,13 +1453,13 @@
         <v>-1.3921</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4284000000000001</v>
+        <v>-0.4283999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-0.9636999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9162999999999998</v>
+        <v>0.9163000000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.7445</v>
@@ -1468,16 +1468,16 @@
         <v>14.6606</v>
       </c>
       <c r="S13" t="n">
-        <v>11.0859</v>
+        <v>11.6363</v>
       </c>
       <c r="T13" t="n">
-        <v>5.754300000000001</v>
+        <v>6.3048</v>
       </c>
       <c r="U13" t="n">
         <v>5.331700000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>2.845499999999999</v>
+        <v>2.8455</v>
       </c>
       <c r="W13" t="n">
         <v>9.2325</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8294</v>
+        <v>2.3763</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2294</v>
+        <v>1.6525</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6</v>
+        <v>0.7238</v>
       </c>
       <c r="G14" t="n">
         <v>4.8087</v>
@@ -1546,13 +1546,13 @@
         <v>0.9163</v>
       </c>
       <c r="S14" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.4444</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6026</v>
+        <v>0.0257</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5939</v>
+        <v>-0.47</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0717</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. CHOFRE TARREGA</t>
+          <t>P. GARCIA BOSCH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3023</v>
+        <v>-0.3883</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4966</v>
+        <v>0.859</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.799</v>
+        <v>-1.2473</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6911</v>
+        <v>0.3286</v>
       </c>
       <c r="H17" t="n">
-        <v>0.511</v>
+        <v>0.3159</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.2021</v>
+        <v>0.0127</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4943</v>
+        <v>2.1682</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3872</v>
+        <v>1.418</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.8814</v>
+        <v>0.7501</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1968</v>
+        <v>-1.8395</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8762</v>
+        <v>-1.1021</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3207</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9163</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3562</v>
+        <v>-0.8573</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0355</v>
+        <v>-0.7436</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3917</v>
+        <v>-0.1137</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8287</v>
+        <v>0.5068</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9554</v>
+        <v>1.267</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1267</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GARCIA BOSCH</t>
+          <t>E. CHOFRE TARREGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7832</v>
+        <v>-0.3955</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6667</v>
+        <v>0.3043</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4499</v>
+        <v>-0.6999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3286</v>
+        <v>-1.6911</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3159</v>
+        <v>0.511</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0127</v>
+        <v>-2.2021</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1682</v>
+        <v>-0.4943</v>
       </c>
       <c r="K18" t="n">
-        <v>1.418</v>
+        <v>1.3872</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7501</v>
+        <v>-1.8814</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8395</v>
+        <v>-1.1968</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1021</v>
+        <v>-0.8762</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.3207</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3665</v>
+        <v>0.9163</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4661</v>
+        <v>0.9163</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2521</v>
+        <v>-0.4495</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9359</v>
+        <v>-0.1568</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3162</v>
+        <v>-0.2926</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5068</v>
+        <v>0.8287</v>
       </c>
       <c r="W18" t="n">
-        <v>1.267</v>
+        <v>0.9554</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7602</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8371</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1343</v>
+        <v>0.2503</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7028</v>
+        <v>-0.8718</v>
       </c>
       <c r="G19" t="n">
         <v>2.0292</v>
@@ -1936,13 +1936,13 @@
         <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4606</v>
+        <v>-1.2451</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8446</v>
+        <v>-0.46</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.616</v>
+        <v>-0.7851</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5889</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8982</v>
+        <v>-2.006</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4308</v>
+        <v>-0.8154</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4674</v>
+        <v>-1.1906</v>
       </c>
       <c r="G20" t="n">
         <v>0.0638</v>
@@ -2014,13 +2014,13 @@
         <v>1.6493</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1845</v>
+        <v>-1.2922</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.405</v>
+        <v>-0.7896</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7795</v>
+        <v>-0.5027</v>
       </c>
       <c r="V20" t="n">
         <v>0.3219</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3891</v>
+        <v>-2.4095</v>
       </c>
       <c r="E21" t="n">
         <v>-1.2367</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1524</v>
+        <v>-1.1728</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6385</v>
@@ -2092,13 +2092,13 @@
         <v>0.5498</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3736</v>
+        <v>-0.394</v>
       </c>
       <c r="T21" t="n">
         <v>-0.4404</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0668</v>
+        <v>0.0464</v>
       </c>
       <c r="V21" t="n">
         <v>-0.0104</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6875</v>
+        <v>-2.4179</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1521</v>
+        <v>-2.0559</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5354</v>
+        <v>-0.362</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0716</v>
@@ -2170,13 +2170,13 @@
         <v>2.0158</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.772</v>
+        <v>-1.5024</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.644</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.128</v>
+        <v>-0.9546</v>
       </c>
       <c r="V22" t="n">
         <v>1.1403</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2197</v>
+        <v>-4.2692</v>
       </c>
       <c r="E23" t="n">
         <v>-4.0765</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1432</v>
+        <v>-0.1927</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4801</v>
@@ -2248,13 +2248,13 @@
         <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2344</v>
+        <v>-0.2839</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3869</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1525</v>
+        <v>0.1029</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9554</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9148</v>
+        <v>-4.3844</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2889</v>
+        <v>-2.8081</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6258</v>
+        <v>-1.5763</v>
       </c>
       <c r="G24" t="n">
         <v>-1.824</v>
@@ -2326,13 +2326,13 @@
         <v>2.7489</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.9353</v>
+        <v>-2.405</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.6153</v>
+        <v>-1.1346</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3199</v>
+        <v>-1.2704</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0717</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.8279</v>
+        <v>-7.8731</v>
       </c>
       <c r="E25" t="n">
         <v>-5.5619</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.266</v>
+        <v>-2.3112</v>
       </c>
       <c r="G25" t="n">
         <v>-3.7077</v>
@@ -2404,13 +2404,13 @@
         <v>1.0995</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5259</v>
+        <v>-1.5711</v>
       </c>
       <c r="T25" t="n">
         <v>-0.6976</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8283</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-0.945</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-21.7551</v>
+        <v>-21.1138</v>
       </c>
       <c r="E26" t="n">
-        <v>-12.2132</v>
+        <v>-12.2131</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.5419</v>
+        <v>-8.9008</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.9074</v>
+        <v>-6.907400000000001</v>
       </c>
       <c r="H26" t="n">
         <v>-6.1055</v>
@@ -2455,7 +2455,7 @@
         <v>-0.8016000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>1.392199999999999</v>
+        <v>1.3922</v>
       </c>
       <c r="K26" t="n">
         <v>0.4282999999999995</v>
@@ -2482,13 +2482,13 @@
         <v>13.7443</v>
       </c>
       <c r="S26" t="n">
-        <v>-11.0859</v>
+        <v>-10.4449</v>
       </c>
       <c r="T26" t="n">
-        <v>-5.3316</v>
+        <v>-5.3317</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.754200000000001</v>
+        <v>-5.113300000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-2.8454</v>
